--- a/astro-site/public/dl/burger-joint-checklist-templates/06-burger-joint-event-checklists.xlsx
+++ b/astro-site/public/dl/burger-joint-checklist-templates/06-burger-joint-event-checklists.xlsx
@@ -1986,7 +1986,7 @@
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>2 weeks out</t>
         </is>
       </c>
       <c r="F13" s="28" t="n"/>
